--- a/p6_deployment/data/england/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_selected.xlsx
@@ -425,111 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:AI45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
@@ -538,906 +603,1386 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.339221377233877</v>
+      </c>
       <c r="D2" t="n">
-        <v>0.1073010289463784</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6534025277866826</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.493842954620736</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9375583437099245</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5066577545699402</v>
+        <v>0.8547223841423679</v>
       </c>
       <c r="I2" t="n">
-        <v>1.070827433757874</v>
+        <v>-0.8547504681941092</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1172513884580411</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>0.7214373174347188</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-1.717048069296657</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1.419827234775901</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.591684454927278</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1.65658516201982</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.068450813679242</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-1.755684538236939</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9999459593089504</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4244779234824463</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2251846759667669</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0.4200171073600391</v>
+      </c>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>-0.1069225458868052</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.02059514550930349</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.08094645182801706</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.5605744317012659</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0757380888767468</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.3568706515130941</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.1713123590511368</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2201965537561206</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.1095533267374549</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-0.3262498635040334</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.7325937928712702</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6112786565284644</v>
+      </c>
       <c r="D3" t="n">
-        <v>0.1010706756852561</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>1.088366449840425</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F3" t="n">
-        <v>1.202001025275109</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4015417613175323</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H3" t="n">
-        <v>1.76039670762367</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.667178681241082</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J3" t="n">
-        <v>1.968397384544237</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.1130998413203891</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.394131153925321</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1.489364742009042</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8450094825587373</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1.412491440463311</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.423586367065355</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.7619342651498524</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-1.902858369180083</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.102136128435901</v>
+      </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0.5376728533978877</v>
+      </c>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0.1687759750365619</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04293169766424557</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.2955315856993013</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.224680195695276</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.1824963169836053</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8834373981983745</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.2770172071917255</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.3262473985508627</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.1946483635440964</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>-0.02189086621451541</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.8723608279222199</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7477679166607292</v>
+      </c>
       <c r="D4" t="n">
-        <v>-1.075220020014698</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01012851130935842</v>
+        <v>1.412237343162496</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.122002405669585</v>
+        <v>1.043272089906375</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.415554452992678</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H4" t="n">
-        <v>2.462452283012659</v>
+        <v>1.397576235676002</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08781661734534275</v>
+        <v>-1.397625998602981</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7058232007129</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.514086898314456</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.75736528618258</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-3.543397539966588</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.451693947822787</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-3.772286330050807</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.851543750145735</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-4.632997469123034</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-6.169641572394721</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.5099851341415469</v>
+      </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>0.2999860090610922</v>
+      </c>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0.8632637639662725</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.681191107250985</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.823882903977213</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04251154927220871</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.389067806344018</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.7962923483468708</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.436185503714945</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.327409193951351</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.958851548668886</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>1.048323461188802</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.4241322989750632</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7477679166607292</v>
+      </c>
       <c r="D5" t="n">
-        <v>-2.006034797226421</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07281286857764682</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8431219939562219</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4024831122710564</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8828272383874337</v>
+        <v>-1.43812085720364</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.451851165417613</v>
+        <v>1.438184337874939</v>
       </c>
       <c r="J5" t="n">
-        <v>2.080128568812217</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+        <v>-0.3696241010989402</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.416307776551107</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7595775587676545</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-2.105574581396306</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.758752563554639</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.276631879911333</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.5616071367219981</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1901125114865394</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.175565777723043</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1208308363061085</v>
+      </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0.6085897532434319</v>
+      </c>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>0.005654240913119119</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.09084701199889168</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.08502513095112638</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5606128400132927</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.2348663173528611</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.7506013293600146</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.1712279639628021</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.7366130498409165</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.06607986635912405</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>0.2809651236809805</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.421869562610451</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.339221377233877</v>
+      </c>
       <c r="D6" t="n">
-        <v>0.4562008115692465</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6736595504053994</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F6" t="n">
-        <v>1.109040888037321</v>
+        <v>0.4746284463236872</v>
       </c>
       <c r="G6" t="n">
-        <v>0.508745077796011</v>
+        <v>2.072004313626362</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3603961763639009</v>
+        <v>0.04044160684191658</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7035339305263067</v>
+        <v>-0.04043717258080222</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5269323974406318</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+        <v>-0.1877805313433304</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.6343830154126764</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.067220434893788</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.3801870311119669</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.374113884096997</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.03298064947228</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.157864321459517</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.9523436204771309</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.599028145432136</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1.502551779089928</v>
+      </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>2.015127519954532</v>
+      </c>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>0.9077991072580649</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.8478122581197975</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5658765894262558</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5749896484515694</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9558371699822161</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2571657053951705</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.022230107186427</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.8903767450305313</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.8280216452514323</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>0.6281598317001345</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.7664524689293419</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>4.236984400630231</v>
+        <v>-0.5109663712257129</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3350540525933289</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5077767906313889</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9231206135617452</v>
+        <v>-0.378337019050345</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4024831122710564</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H7" t="n">
-        <v>1.321611973005552</v>
+        <v>-0.8595529364901612</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.149628744869329</v>
+        <v>0.8595933120444317</v>
       </c>
       <c r="J7" t="n">
-        <v>1.52147264747232</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>-0.1271660080914603</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.7145804268114895</v>
+      </c>
       <c r="L7" t="n">
-        <v>-0.05807288981388329</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4800440104887923</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9120902726072948</v>
+        <v>-0.4777515212869103</v>
       </c>
       <c r="O7" t="n">
-        <v>2.022238623522832</v>
+        <v>-0.2154585555999435</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.407559984095215</v>
+        <v>-0.3227916564190099</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.291366921909828</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.794549569501417</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S7" t="n">
-        <v>1.791415200869481</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.567720146608758</v>
-      </c>
+        <v>1.63883830878714</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>0.7980507722407626</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.379384111074274</v>
+        <v>1.391950605299722</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>0.2016214458213294</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.2173844279976308</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.008734525427169128</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.3204062177587659</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.07155050391685028</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.8024271294775628</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.06630377038931792</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1347672804279295</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.01596627375984602</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0.1411854360369058</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.7580202305561267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.279973750830669</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2630598604744445</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8192852875606926</v>
+        <v>-0.9128948557826102</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.493842954620736</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.206507985859645</v>
-      </c>
+        <v>-0.2835630784532303</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>-1.091704067394098</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09783371288802201</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.495269327763118</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0.2365211314197592</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.215814248054073</v>
+      </c>
       <c r="L8" t="n">
-        <v>-0.9077864267997728</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4681381028225471</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4974250665274114</v>
+        <v>-0.6936425659560193</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6815092041788048</v>
+        <v>-1.533663480955614</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6859002680783363</v>
+        <v>0.453358654565702</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3307743899711487</v>
+        <v>-1.737188523520676</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4383835715159054</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2897558780033413</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.4088613325326073</v>
-      </c>
+        <v>-1.902858369180083</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>-0.8249199010595329</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.8256105452346704</v>
+        <v>-0.1494609623799834</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>-1.702019229805957</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.121592719259533</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.774968428493732</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6581313636404122</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2.336776135242038</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.290660335731659</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-2.386999909447149</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-2.50654007057192</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-2.294709483720588</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>-2.111071143905528</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.01034627875172835</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6112786565284644</v>
+      </c>
       <c r="D9" t="n">
-        <v>-0.8957858460943664</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01012851130935842</v>
+        <v>3.239126928047936</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3783213077672833</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5632880869887741</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8828272383874337</v>
+        <v>-0.1738428082371496</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.049457789442537</v>
+        <v>0.1738557999490154</v>
       </c>
       <c r="J9" t="n">
-        <v>2.638784490152112</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+        <v>-0.3696241010989402</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.61680130504814</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9754746155400137</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6839479095516249</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3500109666974757</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.6921741348686902</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.356963500547597</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.297229033230895</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2826635180325506</v>
+      </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>0.4036928779913588</v>
+      </c>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>0.8988350380610607</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.03460854361411969</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.6216318511659429</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1.343584713116867</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5650166788092272</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.036324216676852</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.137048871339712</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.136971855273077</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.7632839355076233</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>0.8288113188021131</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.7873247669274861</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.056923411754772</v>
+      </c>
       <c r="D10" t="n">
-        <v>-0.3350540525933289</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5077767906313889</v>
+        <v>1.080075600456052</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9231206135617452</v>
+        <v>0.8537242087121459</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4024831122710564</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H10" t="n">
-        <v>1.321611973005552</v>
+        <v>0.3118685326087335</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.149628744869329</v>
+        <v>-0.3118749377852377</v>
       </c>
       <c r="J10" t="n">
-        <v>1.52147264747232</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+        <v>2.418643968487077</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.760640733803758</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-2.872763763804937</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.8775497521556299</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.091813919160445</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1635813362170178</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.221496519509297</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.3513008407383969</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1.616235901390139</v>
+      </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>0.9965706944734934</v>
+      </c>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>-0.004643706591545922</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.255256480912642</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2442604405503135</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.6382886991796844</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.001918145130644</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.4180929661430551</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.068521817842047</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.7478827703562824</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.2476321094246121</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>0.2073177613738873</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.01279366296060563</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.63494810752045</v>
+      </c>
       <c r="D11" t="n">
-        <v>0.2630598604744445</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8192852875606926</v>
+        <v>0.5818329863963865</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.493842954620736</v>
+        <v>0.5694023869208018</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.206507985859645</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.091704067394098</v>
+        <v>1.669003161442819</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09783371288802201</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1.495269327763118</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+        <v>-1.669063763807416</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>-0.915073955308523</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2147263603817656</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.440313973089069</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.434426302925192</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.451574971172967</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.03543156403547253</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.428016124263538</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.079150508807505</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-2.286354170896134</v>
+      </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>-0.825678265638909</v>
+      </c>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>0.01523128539329692</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.7022653239953391</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.06845853396118692</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.2564630298969067</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.3825368480914692</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1.612302034315884</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.989225599426537</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.06334596971671</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1189008731933365</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>0.1133797992474932</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.352012525075538</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C12" t="n">
-        <v>1.650910267132934</v>
+        <v>1.63494810752045</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8957858460943664</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.01012851130935842</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.3783213077672833</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.5632880869887741</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.8828272383874337</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-1.049457789442537</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.638784490152112</v>
-      </c>
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>-0.2350320538613501</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.01562828151997313</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.138619523539658</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.892858218167583</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.3965893059469824</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.124824145882247</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.1525681294656875</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1.407577539820226</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.751242041084851</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.640684030903745</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.598047788375014</v>
-      </c>
+        <v>-2.859456995012502</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5903539818980568</v>
+        <v>-0.7763621548162278</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1010706756852561</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E13" t="n">
-        <v>1.088366449840425</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F13" t="n">
-        <v>1.202001025275109</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4015417613175323</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.76039670762367</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-1.667178681241082</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.968397384544237</v>
-      </c>
+        <v>0.42468057404869</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0.5037595581385397</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-0.6229433458121535</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.3967453994463608</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.8226325843956603</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-1.046730126086776</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.2251261091430794</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-1.133601359760289</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-0.8868366840799572</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.2168958051394266</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-0.706885670274057</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.1347799745430973</v>
-      </c>
+        <v>-0.287486390661077</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C14" t="n">
-        <v>0.444075671500862</v>
+        <v>1.65011358086848</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.075220020014698</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01012851130935842</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.122002405669585</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.415554452992678</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.462452283012659</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.08781661734534275</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.7058232007129</v>
-      </c>
+        <v>0.0007587433381137274</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>1.001515247564158</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.4026413889939891</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.4590317707425678</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.1465855399322515</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.118249021963862</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.5826919492626554</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.1126050862142352</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.4479833871970932</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.610386511827705</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.05444735133588</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.05497460396137835</v>
-      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7888855559671684</v>
+        <v>1.65011358086848</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1073010289463784</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.6534025277866826</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.493842954620736</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.9375583437099245</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5066577545699402</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.070827433757874</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.1172513884580411</v>
-      </c>
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>0.8380730808870869</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.8864077733365094</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.7491242342300378</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.57028745220675</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.757419163955422</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.4610739363257644</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-1.090729043452758</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.3844850443520343</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.5160792128677493</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.2583555932892478</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-1.739530555990936</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.107568808597516</v>
+        <v>1.65011358086848</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5322111213549426</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2589526509703737</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F16" t="n">
-        <v>1.387921299750684</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.1764147967127277</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.530488802012216</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.750654477430075</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.3779574850833262</v>
-      </c>
+        <v>-0.1887891378561156</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>-0.7600281043998113</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-0.6519693288727048</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-1.35320223671634</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.8649872644048137</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.118249021963862</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.123919076039651</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.9936065320912348</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.005093778294109235</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.6873421007653234</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-1.123939952382739</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-3.858917699578866</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8994226501410234</v>
+      </c>
       <c r="D17" t="n">
-        <v>0.5322111213549426</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2589526509703737</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F17" t="n">
-        <v>1.387921299750684</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1764147967127277</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.530488802012216</v>
+        <v>-1.973831894901305</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.750654477430075</v>
+        <v>1.973916769199483</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3779574850833262</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+        <v>0.7214373174347188</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.08739368717664438</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.824104133701805</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1.855341996794555</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.484547863495486</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.994500018539928</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.666027818422636</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5.079150508807505</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.241284315154525</v>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>0.8668528759609205</v>
+      </c>
       <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1124260843452994</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.03317029857163505</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.3209509821939799</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.1865669192197163</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.094826528701418</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.9898919689781894</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.07814358019152451</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.0147188975109438</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.09327751366901972</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.4816151504244152</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.559120740780303</v>
+      </c>
       <c r="D18" t="n">
-        <v>1.963946300760925</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E18" t="n">
-        <v>1.00542506995342</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4712814450050707</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.5632880869887741</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.6634348710783747</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.04774823517462645</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.9628167261324243</v>
-      </c>
+        <v>-0.1887891378561156</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1446,213 +1991,1475 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>-3.044872614579567</v>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5903539818980568</v>
+        <v>1.65011358086848</v>
       </c>
       <c r="D19" t="n">
-        <v>1.963946300760925</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E19" t="n">
-        <v>1.00542506995342</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4712814450050707</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5632880869887741</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.6634348710783747</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.04774823517462645</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.9628167261324243</v>
-      </c>
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>-1.618099479454419</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-1.145411040902075</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.2529173036162889</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.4530128157736298</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-0.6859002680783363</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1.872848000131962</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.09117073821045693</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.2766332229247345</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.4899976920996834</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-1.297056824201437</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.1927264699894117</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C20" t="n">
-        <v>3.547364631697618</v>
+        <v>1.65011358086848</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.006034797226421</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.07281286857764682</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8431219939562219</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4024831122710564</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.8828272383874337</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-2.451851165417613</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.080128568812217</v>
-      </c>
+        <v>0.42468057404869</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
-        <v>-0.01628369947031781</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.176667603942021</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.2325025198102043</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.378741344255939</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.03575944793854285</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.3243820096686</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-0.7525141036933332</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.9905231581032496</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.552944999684525</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.535764714649988</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.48394275637266</v>
-      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4816151504244152</v>
+        <v>1.864158782823006</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.9351638663643629</v>
+        <v>1.65011358086848</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4562008115692465</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6736595504053994</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F21" t="n">
-        <v>1.109040888037321</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.508745077796011</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.3603961763639009</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.7035339305263067</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.5269323974406318</v>
-      </c>
+        <v>0.2850805651294578</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
-        <v>0.5037595581385397</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-0.4358870105330456</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.2073326030399413</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-1.221729142328788</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.56156845399762</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-0.8149956770997987</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-1.667123518254028</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.208341733505831</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.3448405385836202</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.7777062087453425</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.6552186788224842</v>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.225480327123656</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>-3.0212742629983</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2850805651294578</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.42468057404869</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.020746436925259</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>-2.85758410996637</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.056923411754772</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>-2.461937143971006</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.9962615183626544</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2496712436899428</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3798545057265725</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.626146278427006</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-1.626205169301453</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.516554540799623</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.849279955539432</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.777110500812665</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-1.596085441209226</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.11010122539892</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-5.188358088827596</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-3.066526515511348</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-4.133767980400661</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>-0.3768074434696565</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.2396364553311822</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.0809611601273143</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.5733138358562849</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.5527583140049219</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-0.3800112158896825</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.540340432185463</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-0.4848878936342016</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-0.08565480062896462</v>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>-0.4506622512937416</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.7468139844293883</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.1887891378561156</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.013163700251244</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>-2.971127765888117</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.559120740780303</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>-2.176790395697422</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.864158782823006</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.65011358086848</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6112786565284644</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.4607755271036255</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5818329863963865</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5694023869208018</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-1.6344741004234</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.7738391704585348</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.7738761230325046</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-0.1271660080914603</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.9896145654132948</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-1.419827234775901</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.207894294314541</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.2687141605755519</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.348762330755255</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.468324445853402</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.070998583024891</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.315438661270752</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-0.4416794557715791</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>0.9690772555367683</v>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="n">
+        <v>-0.9519709152180151</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-1.138763478404397</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-1.751939068741641</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>-0.1727353274942171</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-1.138806951749114</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>-1.026275827575905</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-0.7084343493782925</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>-0.8701715832817006</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>-1.810429370203789</v>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="n">
+        <v>-1.267038554199874</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.646850346543564</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI45"/>
+  <dimension ref="A1:AI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,1080 +603,1128 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C2" t="n">
-        <v>1.339221377233877</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.9128948557826102</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09401519725900095</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.398981295740146</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8547223841423679</v>
+        <v>-1.073837351569227</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8547504681941092</v>
+        <v>1.073886284574249</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.4908531476026803</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.717048069296657</v>
+        <v>0.154224863342322</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.419827234775901</v>
+        <v>0.5779604926390248</v>
       </c>
       <c r="M2" t="n">
-        <v>1.591684454927278</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.65658516201982</v>
+        <v>-1.434982714052587</v>
       </c>
       <c r="O2" t="n">
-        <v>2.068450813679242</v>
+        <v>-0.7491051177680702</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.755684538236939</v>
+        <v>-0.6810148768734923</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999459593089504</v>
+        <v>-1.300833750895663</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4244779234824463</v>
+        <v>-2.678637133400926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2251846759667669</v>
+        <v>-2.269498205480952</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>0.4200171073600391</v>
+        <v>-0.6871542357414602</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-0.1069225458868052</v>
+        <v>-0.5067488174867379</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02059514550930349</v>
+        <v>-0.9652684969024259</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.08094645182801706</v>
+        <v>-1.140872329406872</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.5605744317012659</v>
+        <v>0.6087226979006948</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0757380888767468</v>
+        <v>-1.113457414810803</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3568706515130941</v>
+        <v>0.742400770640682</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1713123590511368</v>
+        <v>-1.424054881920683</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2201965537561206</v>
+        <v>-1.327229436810696</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1095533267374549</v>
+        <v>-1.473066010663299</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>-0.3262498635040334</v>
+        <v>-0.8937778012825365</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.7325937928712702</v>
+        <v>-0.3162826722544151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.597034424150377</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4146522417229446</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007587433381137274</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8365115089431081</v>
+        <v>-2.869966905106654</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5166978723636554</v>
+        <v>-0.5452691277075311</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5167245559967235</v>
+        <v>0.5452969523340327</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.4789792244272392</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1130998413203891</v>
+        <v>1.357186034324523</v>
       </c>
       <c r="L3" t="n">
-        <v>2.394131153925321</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.489364742009042</v>
+        <v>0.7700713357442589</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8450094825587373</v>
+        <v>0.3058530112157789</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.412491440463311</v>
+        <v>1.706158652207303</v>
       </c>
       <c r="P3" t="n">
-        <v>2.423586367065355</v>
+        <v>1.050397355323173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7619342651498524</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.902858369180083</v>
+        <v>0.7638811328290654</v>
       </c>
       <c r="S3" t="n">
-        <v>0.102136128435901</v>
+        <v>0.5268440273970857</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>0.5376728533978877</v>
+        <v>0.3579210191733655</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0.1687759750365619</v>
+        <v>-1.106858076392562</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.04293169766424557</v>
+        <v>-1.354542963909153</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.2955315856993013</v>
+        <v>-1.972777787779417</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.224680195695276</v>
+        <v>-0.5485138088277345</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1824963169836053</v>
+        <v>-1.38506990523568</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8834373981983745</v>
+        <v>-1.608277485709562</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.2770172071917255</v>
+        <v>-0.8661300883957506</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3262473985508627</v>
+        <v>-0.8706994021482716</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1946483635440964</v>
+        <v>-2.051055713682274</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-0.02189086621451541</v>
+        <v>-1.696491604387708</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.8723608279222199</v>
+        <v>1.303318242912968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7477679166607292</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>1.412237343162496</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F4" t="n">
-        <v>1.043272089906375</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48383524852078</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H4" t="n">
-        <v>1.397576235676002</v>
+        <v>0.8547223841423679</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.397625998602981</v>
+        <v>-0.8547504681941092</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.514086898314456</v>
+        <v>-1.717048069296657</v>
       </c>
       <c r="L4" t="n">
-        <v>2.75736528618258</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.543397539966588</v>
+        <v>1.591684454927278</v>
       </c>
       <c r="N4" t="n">
-        <v>3.451693947822787</v>
+        <v>-1.65658516201982</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.772286330050807</v>
+        <v>2.068450813679242</v>
       </c>
       <c r="P4" t="n">
-        <v>4.851543750145735</v>
+        <v>-1.755684538236939</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.632997469123034</v>
+        <v>0.9999459593089504</v>
       </c>
       <c r="R4" t="n">
-        <v>-6.169641572394721</v>
+        <v>0.4244779234824463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5099851341415469</v>
+        <v>0.2251846759667669</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>0.2999860090610922</v>
+        <v>0.3860546239676479</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>0.8632637639662725</v>
+        <v>-0.1153306758532679</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.681191107250985</v>
+        <v>0.1499771036719323</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.823882903977213</v>
+        <v>-0.09600647132601053</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04251154927220871</v>
+        <v>-0.6514819160798689</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.389067806344018</v>
+        <v>-0.01538065793583716</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.7962923483468708</v>
+        <v>0.1491520137674208</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.436185503714945</v>
+        <v>-0.1898792784850098</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.327409193951351</v>
+        <v>0.2924175502188048</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.958851548668886</v>
+        <v>0.03353041487183422</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>1.048323461188802</v>
+        <v>-0.3087147772404399</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.4241322989750632</v>
+        <v>-1.012733153077933</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7477679166607292</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D5" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1903066245323431</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.43812085720364</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I5" t="n">
-        <v>1.438184337874939</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3696241010989402</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.416307776551107</v>
+        <v>-0.1130998413203891</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7595775587676545</v>
+        <v>2.394131153925321</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.105574581396306</v>
+        <v>-1.489364742009042</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.758752563554639</v>
+        <v>0.8450094825587373</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.276631879911333</v>
+        <v>-1.412491440463311</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5616071367219981</v>
+        <v>2.423586367065355</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1901125114865394</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.175565777723043</v>
+        <v>-1.902858369180083</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1208308363061085</v>
+        <v>0.102136128435901</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>0.6085897532434319</v>
+        <v>0.2045170639298238</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>0.005654240913119119</v>
+        <v>-0.001049863446294658</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.09084701199889168</v>
+        <v>-0.0592666405379092</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.08502513095112638</v>
+        <v>-0.269705091115608</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5606128400132927</v>
+        <v>1.395063588347172</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2348663173528611</v>
+        <v>-0.1293760262886053</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7506013293600146</v>
+        <v>0.8984969994349373</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.1712279639628021</v>
+        <v>-0.2563404105494574</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.7366130498409165</v>
+        <v>-0.4821140983654975</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.06607986635912405</v>
+        <v>-0.3906600473146071</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0.2809651236809805</v>
+        <v>-0.001850767627551133</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.421869562610451</v>
+        <v>-0.6166039312400379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C6" t="n">
-        <v>1.339221377233877</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4157521150431646</v>
+        <v>1.412237343162496</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4746284463236872</v>
+        <v>1.043272089906375</v>
       </c>
       <c r="G6" t="n">
-        <v>2.072004313626362</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04044160684191658</v>
+        <v>1.397576235676002</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04043717258080222</v>
+        <v>-1.397625998602981</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1877805313433304</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6343830154126764</v>
+        <v>-0.514086898314456</v>
       </c>
       <c r="L6" t="n">
-        <v>2.067220434893788</v>
+        <v>2.75736528618258</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3801870311119669</v>
+        <v>-3.543397539966588</v>
       </c>
       <c r="N6" t="n">
-        <v>1.374113884096997</v>
+        <v>3.451693947822787</v>
       </c>
       <c r="O6" t="n">
-        <v>1.03298064947228</v>
+        <v>-3.772286330050807</v>
       </c>
       <c r="P6" t="n">
-        <v>1.157864321459517</v>
+        <v>4.851543750145735</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9523436204771309</v>
+        <v>-4.632997469123034</v>
       </c>
       <c r="R6" t="n">
-        <v>0.599028145432136</v>
+        <v>-6.169641572394721</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.502551779089928</v>
+        <v>-0.5099851341415469</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>2.015127519954532</v>
+        <v>0.0382030972248047</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>0.9077991072580649</v>
+        <v>0.8964088007959791</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8478122581197975</v>
+        <v>1.8158076357542</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5658765894262558</v>
+        <v>1.753498562586212</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5749896484515694</v>
+        <v>0.2298982358676154</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9558371699822161</v>
+        <v>1.309215041702351</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2571657053951705</v>
+        <v>-0.9757525964158894</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.022230107186427</v>
+        <v>1.412912385952343</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.8903767450305313</v>
+        <v>1.32187707335843</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.8280216452514323</v>
+        <v>2.005340974004832</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>0.6281598317001345</v>
+        <v>0.9784788467559364</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.7664524689293419</v>
+        <v>-0.4530376284776874</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.5109663712257129</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.078975727135832</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.378337019050345</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.222643165528982</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8595529364901612</v>
+        <v>-1.43812085720364</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8595933120444317</v>
+        <v>1.438184337874939</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1271660080914603</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7145804268114895</v>
+        <v>-1.416307776551107</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05769923881117887</v>
+        <v>0.7595775587676545</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9754746155400137</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4777515212869103</v>
+        <v>-0.758752563554639</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2154585555999435</v>
+        <v>-1.276631879911333</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3227916564190099</v>
+        <v>-0.5616071367219981</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9041475939638333</v>
+        <v>-0.1901125114865394</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.157356149683186</v>
+        <v>-1.175565777723043</v>
       </c>
       <c r="S7" t="n">
-        <v>1.63883830878714</v>
+        <v>-0.1208308363061085</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>1.391950605299722</v>
+        <v>0.7353381006551266</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>0.2016214458213294</v>
+        <v>-0.009017550057460712</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2173844279976308</v>
+        <v>-0.01425754571295434</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008734525427169128</v>
+        <v>0.0722202347974373</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3204062177587659</v>
+        <v>0.6584010503112059</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.07155050391685028</v>
+        <v>0.234086530441603</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8024271294775628</v>
+        <v>0.8121783655272882</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.06630377038931792</v>
+        <v>-0.1944272360231096</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1347672804279295</v>
+        <v>-0.7347842240107532</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01596627375984602</v>
+        <v>-0.09221436003096149</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>0.1411854360369058</v>
+        <v>0.2563046690309104</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.7580202305561267</v>
+        <v>2.222555270959666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>1.013163700251244</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9128948557826102</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2835630784532303</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>0.4746284463236872</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.072004313626362</v>
+      </c>
       <c r="H8" t="n">
-        <v>-0.5166978723636554</v>
+        <v>0.04044160684191658</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5167245559967235</v>
+        <v>-0.04043717258080222</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2365211314197592</v>
+        <v>-0.5150989569034282</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.215814248054073</v>
+        <v>-0.6343830154126764</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3301248380041233</v>
+        <v>2.067220434893788</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.105574581396306</v>
+        <v>-0.3801870311119669</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6936425659560193</v>
+        <v>1.374113884096997</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.533663480955614</v>
+        <v>1.03298064947228</v>
       </c>
       <c r="P8" t="n">
-        <v>0.453358654565702</v>
+        <v>1.157864321459517</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.737188523520676</v>
+        <v>0.9523436204771309</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.902858369180083</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <v>0.599028145432136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.502551779089928</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>-0.1494609623799834</v>
+        <v>2.267414477793932</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>-1.702019229805957</v>
+        <v>0.7032684144555752</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.121592719259533</v>
+        <v>0.4362924602504121</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.774968428493732</v>
+        <v>0.5591242699344914</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6581313636404122</v>
+        <v>0.4237930952118625</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.336776135242038</v>
+        <v>0.9616852167439753</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.290660335731659</v>
+        <v>0.4959502632513858</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.386999909447149</v>
+        <v>0.9682664038348333</v>
       </c>
       <c r="AE8" t="n">
-        <v>-2.50654007057192</v>
+        <v>0.5486030459394262</v>
       </c>
       <c r="AF8" t="n">
-        <v>-2.294709483720588</v>
+        <v>0.5727515272097295</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>-2.111071143905528</v>
+        <v>0.6570927240350641</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.01034627875172835</v>
+        <v>0.7050226511682707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6112786565284644</v>
+        <v>-0.5109663712257129</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>3.239126928047936</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F9" t="n">
-        <v>2.085785436474636</v>
+        <v>-0.378337019050345</v>
       </c>
       <c r="G9" t="n">
-        <v>1.248342443837526</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1738428082371496</v>
+        <v>-0.8595529364901612</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1738557999490154</v>
+        <v>0.8595933120444317</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3696241010989402</v>
+        <v>0.5395937476791089</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.61680130504814</v>
+        <v>-0.7145804268114895</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M9" t="n">
         <v>0.9754746155400137</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6839479095516249</v>
+        <v>-0.4777515212869103</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3500109666974757</v>
+        <v>-0.2154585555999435</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6921741348686902</v>
+        <v>-0.3227916564190099</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.356963500547597</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R9" t="n">
-        <v>1.297229033230895</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2826635180325506</v>
+        <v>1.63883830878714</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>0.4036928779913588</v>
+        <v>1.448433449703462</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>0.8988350380610607</v>
+        <v>0.2315198564771405</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.03460854361411969</v>
+        <v>0.1238264763500759</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6216318511659429</v>
+        <v>0.002264280617113906</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.343584713116867</v>
+        <v>0.3352983644899755</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5650166788092272</v>
+        <v>-0.01780402886170527</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.036324216676852</v>
+        <v>0.440269684567982</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.137048871339712</v>
+        <v>-0.04657641849082675</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.136971855273077</v>
+        <v>-0.009910787809691764</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.7632839355076233</v>
+        <v>-0.04359353315900963</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>0.8288113188021131</v>
+        <v>0.1480742199261749</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.7873247669274861</v>
+        <v>0.5631019837845922</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.056923411754772</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D10" t="n">
-        <v>2.393718654096563</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>1.080075600456052</v>
+        <v>-0.9128948557826102</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8537242087121459</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8365115089431081</v>
-      </c>
+        <v>-0.2835630784532303</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.3118685326087335</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3118749377852377</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J10" t="n">
-        <v>2.418643968487077</v>
+        <v>1.266968026701548</v>
       </c>
       <c r="K10" t="n">
-        <v>2.760640733803758</v>
+        <v>-1.215814248054073</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.872763763804937</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3592647761527498</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8775497521556299</v>
+        <v>-0.6936425659560193</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.091813919160445</v>
+        <v>-1.533663480955614</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1635813362170178</v>
+        <v>0.453358654565702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.221496519509297</v>
+        <v>-1.737188523520676</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.3513008407383969</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1.616235901390139</v>
-      </c>
+        <v>-1.902858369180083</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>0.9965706944734934</v>
+        <v>-0.2934376330469567</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-0.004643706591545922</v>
+        <v>-1.496668434824395</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.255256480912642</v>
+        <v>-2.062918259884379</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2442604405503135</v>
+        <v>-1.673355311458964</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6382886991796844</v>
+        <v>0.6605647709671663</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.001918145130644</v>
+        <v>-2.284838449558866</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.4180929661430551</v>
+        <v>0.3319444149836105</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.068521817842047</v>
+        <v>-2.336837578817556</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.7478827703562824</v>
+        <v>-2.537318296389998</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2476321094246121</v>
+        <v>-2.214252909434993</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>0.2073177613738873</v>
+        <v>-2.010369648506034</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.01279366296060563</v>
+        <v>-0.06093380452166856</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C11" t="n">
-        <v>1.63494810752045</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D11" t="n">
-        <v>2.393718654096563</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5818329863963865</v>
+        <v>3.239126928047936</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5694023869208018</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01284963915427201</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H11" t="n">
-        <v>1.669003161442819</v>
+        <v>-0.1738428082371496</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.669063763807416</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
+        <v>0.1738557999490154</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.3696241010989402</v>
+      </c>
       <c r="K11" t="n">
-        <v>-0.915073955308523</v>
+        <v>-1.61680130504814</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2147263603817656</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M11" t="n">
-        <v>3.440313973089069</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N11" t="n">
-        <v>1.434426302925192</v>
+        <v>0.6839479095516249</v>
       </c>
       <c r="O11" t="n">
-        <v>1.451574971172967</v>
+        <v>0.3500109666974757</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03543156403547253</v>
+        <v>0.6921741348686902</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.428016124263538</v>
+        <v>1.356963500547597</v>
       </c>
       <c r="R11" t="n">
-        <v>5.079150508807505</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.286354170896134</v>
+        <v>0.2390627541586076</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>-0.825678265638909</v>
+        <v>0.3228803617050509</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>0.01523128539329692</v>
+        <v>1.010121021362002</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7022653239953391</v>
+        <v>0.05328408987608018</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.06845853396118692</v>
+        <v>0.64220962519623</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.2564630298969067</v>
+        <v>-1.349027811219843</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3825368480914692</v>
+        <v>0.5257096023916737</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.612302034315884</v>
+        <v>-1.110488425295298</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.989225599426537</v>
+        <v>1.117031411325065</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06334596971671</v>
+        <v>1.21503172483887</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1189008731933365</v>
+        <v>0.8188214412314514</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>0.1133797992474932</v>
+        <v>0.854237193884324</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.352012525075538</v>
+        <v>0.736720046983518</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C12" t="n">
-        <v>1.63494810752045</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D12" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>1.080075600456052</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8537242087121459</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8365115089431081</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3118685326087335</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.3118749377852377</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.903560154502037</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.760640733803758</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-2.872763763804937</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.8775497521556299</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.091813919160445</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.1635813362170178</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.221496519509297</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.3513008407383969</v>
+      </c>
       <c r="S12" t="n">
-        <v>-2.859456995012502</v>
+        <v>-1.616235901390139</v>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>0.9417216513541262</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.1040160957581647</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.410538204989231</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.2300262513629699</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.901341387509475</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8489564409995877</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.5597232441256664</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9716201126751248</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.7238307244034425</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2336690314343652</v>
+      </c>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>0.1903662291174423</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.3713497196330051</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.7763621548162278</v>
+        <v>1.63494810752045</v>
       </c>
       <c r="D13" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E13" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.42468057404869</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1689,7 +1737,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-0.287486390661077</v>
+        <v>-2.859456995012502</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -1711,72 +1759,128 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C14" t="n">
-        <v>1.65011358086848</v>
+        <v>1.63494810752045</v>
       </c>
       <c r="D14" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.5818329863963865</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0007587433381137274</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+        <v>0.5694023869208018</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.669003161442819</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.669063763807416</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.915073955308523</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2147263603817656</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.440313973089069</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.434426302925192</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.451574971172967</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.03543156403547253</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.428016124263538</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.079150508807505</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-2.286354170896134</v>
+      </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>-1.337339250556195</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.003196817750909093</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.6967633721998642</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.07357918039973244</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.02586108042951074</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5007488818552442</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.267359271509478</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9355292244728864</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.9431595477319474</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.08125773525704162</v>
+      </c>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>0.1171373177325492</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-1.134291827673825</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C15" t="n">
-        <v>1.65011358086848</v>
+        <v>-0.7763621548162278</v>
       </c>
       <c r="D15" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.42468057404869</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1788,7 +1892,9 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>-0.287486390661077</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1809,14 +1915,14 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C16" t="n">
-        <v>1.65011358086848</v>
+        <v>1.559120740780303</v>
       </c>
       <c r="D16" t="n">
         <v>2.393718654096563</v>
@@ -1839,7 +1945,9 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-3.044872614579567</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1860,181 +1968,179 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8994226501410234</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D17" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G17" t="n">
         <v>-0.398981295740146</v>
       </c>
-      <c r="H17" t="n">
-        <v>-1.973831894901305</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.973916769199483</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.7214373174347188</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.08739368717664438</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.824104133701805</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-1.855341996794555</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4.484547863495486</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-1.994500018539928</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.666027818422636</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5.079150508807505</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-1.241284315154525</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
-        <v>0.8668528759609205</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.1124260843452994</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-0.03317029857163505</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.3209509821939799</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.1865669192197163</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.094826528701418</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-0.9898919689781894</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-0.07814358019152451</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-0.0147188975109438</v>
-      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.09327751366901972</v>
-      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C18" t="n">
-        <v>1.559120740780303</v>
+        <v>0.8994226501410234</v>
       </c>
       <c r="D18" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1887891378561156</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.973831894901305</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.973916769199483</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7214373174347188</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.08739368717664438</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.824104133701805</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.855341996794555</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.484547863495486</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.994500018539928</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.666027818422636</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5.079150508807505</v>
+      </c>
       <c r="S18" t="n">
-        <v>-3.044872614579567</v>
+        <v>-1.241284315154525</v>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>0.8611545575048254</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.04476414701330287</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.04737847572472226</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.3639747202648466</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.05088238108044116</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.407969587555722</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.226265615173698</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.1010456084763366</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.01447896013977084</v>
+      </c>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.1491037240698987</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C19" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D19" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1887891378561156</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.398981295740146</v>
-      </c>
+        <v>0.0007587433381137274</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -2067,27 +2173,25 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C20" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D20" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.42468057404869</v>
-      </c>
+        <v>-0.1887891378561156</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -2124,10 +2228,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C21" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D21" t="n">
         <v>2.393718654096563</v>
@@ -2175,7 +2279,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C22" t="n">
         <v>1.225480327123656</v>
@@ -2224,27 +2328,21 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C23" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D23" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.08359037233672091</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.2850805651294578</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.42468057404869</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -2277,26 +2375,26 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C24" t="n">
-        <v>1.020746436925259</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D24" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5807331130761665</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.09401519725900095</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.42468057404869</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -2309,9 +2407,7 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>-2.85758410996637</v>
-      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2336,10 +2432,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C25" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D25" t="n">
         <v>2.393718654096563</v>
@@ -2383,25 +2479,27 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.056923411754772</v>
+        <v>1.020746436925259</v>
       </c>
       <c r="D26" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.398981295740146</v>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -2414,7 +2512,7 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>-2.461937143971006</v>
+        <v>-2.85758410996637</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -2436,21 +2534,27 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C27" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D27" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.42468057404869</v>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2483,14 +2587,14 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C28" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D28" t="n">
         <v>2.393718654096563</v>
@@ -2530,20 +2634,24 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C29" t="n">
-        <v>1.65011358086848</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D29" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.09553268393522843</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2556,7 +2664,9 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>-2.461937143971006</v>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2577,61 +2687,115 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C30" t="n">
-        <v>1.65011358086848</v>
+        <v>-0.9962615183626544</v>
       </c>
       <c r="D30" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0.2496712436899428</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.3798545057265725</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.626146278427006</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-1.626205169301453</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1.516554540799623</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.849279955539432</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.777110500812665</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1.596085441209226</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.11010122539892</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-5.188358088827596</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-3.066526515511348</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-4.133767980400661</v>
+      </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>-0.6483253687333674</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.4442004294320974</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.08147985949313452</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.5279436335292526</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.5410425272638165</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-0.3035740028029867</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-0.5357857347618424</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-0.6631304724287659</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0.1011952941460156</v>
+      </c>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
+      <c r="AH30" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.06232152976493142</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C31" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D31" t="n">
         <v>2.393718654096563</v>
@@ -2671,115 +2835,61 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.9962615183626544</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D32" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E32" t="n">
-        <v>0.2496712436899428</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.3798545057265725</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.626146278427006</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-1.626205169301453</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-1.516554540799623</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.849279955539432</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.777110500812665</v>
-      </c>
-      <c r="O32" t="n">
-        <v>-1.596085441209226</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.11010122539892</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-5.188358088827596</v>
-      </c>
-      <c r="R32" t="n">
-        <v>-3.066526515511348</v>
-      </c>
-      <c r="S32" t="n">
-        <v>-4.133767980400661</v>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="n">
-        <v>-0.3768074434696565</v>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>-0.2396364553311822</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>-0.0809611601273143</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.5733138358562849</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-0.5527583140049219</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>-0.3800112158896825</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>-0.540340432185463</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>-0.4848878936342016</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>-0.08565480062896462</v>
-      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>-0.4506622512937416</v>
-      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C33" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D33" t="n">
         <v>2.393718654096563</v>
@@ -2819,14 +2929,14 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C34" t="n">
-        <v>1.65011358086848</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D34" t="n">
         <v>2.393718654096563</v>
@@ -2845,7 +2955,9 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>-2.971127765888117</v>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
@@ -2870,10 +2982,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C35" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D35" t="n">
         <v>2.393718654096563</v>
@@ -2913,24 +3025,20 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C36" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D36" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E36" t="n">
-        <v>-0.08249049901650093</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.1903066245323431</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2964,23 +3072,23 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C37" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D37" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1887891378561156</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -3015,14 +3123,14 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C38" t="n">
-        <v>1.013163700251244</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D38" t="n">
         <v>2.393718654096563</v>
@@ -3041,9 +3149,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>-2.971127765888117</v>
-      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
@@ -3064,23 +3170,23 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C39" t="n">
-        <v>1.65011358086848</v>
+        <v>1.559120740780303</v>
       </c>
       <c r="D39" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F39" t="n">
-        <v>0.09553268393522843</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -3094,7 +3200,9 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>-2.176790395697422</v>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
@@ -3115,23 +3223,23 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C40" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D40" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F40" t="n">
-        <v>0.09553268393522843</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -3166,23 +3274,23 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.864158782823006</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C41" t="n">
-        <v>1.559120740780303</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D41" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.09401519725900095</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -3196,9 +3304,7 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>-2.176790395697422</v>
-      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
@@ -3219,20 +3325,24 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C42" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D42" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>-0.2485713703697228</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.09553268393522843</v>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -3266,14 +3376,14 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C43" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D43" t="n">
         <v>2.393718654096563</v>
@@ -3313,24 +3423,20 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.864158782823006</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C44" t="n">
-        <v>1.65011358086848</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D44" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E44" t="n">
-        <v>-0.5807331130761665</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.09401519725900095</v>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -3364,102 +3470,200 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.819875174399046</v>
+        <v>1.886300587034986</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.657696317542495</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4607755271036255</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5818329863963865</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5694023869208018</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-1.6344741004234</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-0.7738391704585348</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.7738761230325046</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-0.1271660080914603</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.9896145654132948</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-1.419827234775901</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.207894294314541</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.2687141605755519</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.348762330755255</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.468324445853402</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.070998583024891</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2.315438661270752</v>
-      </c>
-      <c r="S45" t="n">
-        <v>-0.4416794557715791</v>
-      </c>
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="n">
-        <v>0.9690772555367683</v>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
-      <c r="X45" t="n">
-        <v>-0.9519709152180151</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>-1.138763478404397</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>-1.751939068741641</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>-0.1727353274942171</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-1.138806951749114</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>-1.026275827575905</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>-0.7084343493782925</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>-0.8701715832817006</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>-1.810429370203789</v>
-      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="n">
-        <v>-1.267038554199874</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.646850346543564</v>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.657696317542495</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.6112786565284644</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4607755271036255</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5818329863963865</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5694023869208018</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-1.6344741004234</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.7738391704585348</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.7738761230325046</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.3577501779234991</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9896145654132948</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-1.419827234775901</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.207894294314541</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-0.2687141605755519</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.348762330755255</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.468324445853402</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.070998583024891</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.315438661270752</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-0.4416794557715791</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>1.17709746631509</v>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="n">
+        <v>-0.7582629159433542</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-0.9838590465919386</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-1.646591034896806</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-0.1275690530045329</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-1.055394524480779</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>-0.8748575956025506</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-0.643766612940987</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>-0.7966809484792116</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>-1.769863154857676</v>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="n">
+        <v>-1.128480060063442</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.587196400350206</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_selected.xlsx
@@ -616,7 +616,7 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9128948557826102</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2835630784532303</v>
@@ -631,7 +631,7 @@
         <v>1.073886284574249</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4908531476026803</v>
+        <v>-1.21822742662512</v>
       </c>
       <c r="K2" t="n">
         <v>0.154224863342322</v>
@@ -662,43 +662,43 @@
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-0.6871542357414602</v>
+        <v>-0.8013182701104554</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-0.5067488174867379</v>
+        <v>-0.4932177052508289</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.9652684969024259</v>
+        <v>-0.9100212713517273</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.140872329406872</v>
+        <v>-1.132211386953151</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6087226979006948</v>
+        <v>0.6043327666503044</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.113457414810803</v>
+        <v>-1.108078608409123</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.742400770640682</v>
+        <v>0.8422089578672457</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.424054881920683</v>
+        <v>-1.443289510510791</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.327229436810696</v>
+        <v>-1.269927750938855</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.473066010663299</v>
+        <v>-1.434789898782155</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>-0.8937778012825365</v>
+        <v>-0.8090238902893245</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.3162826722544151</v>
+        <v>-0.1858797637867726</v>
       </c>
     </row>
     <row r="3">
@@ -717,7 +717,7 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08249049901650093</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F3" t="n">
         <v>0.1903066245323431</v>
@@ -732,7 +732,7 @@
         <v>0.5452969523340327</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4789792244272392</v>
+        <v>0.2971356546716294</v>
       </c>
       <c r="K3" t="n">
         <v>1.357186034324523</v>
@@ -763,43 +763,43 @@
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>0.3579210191733655</v>
+        <v>0.4219651718836091</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-1.106858076392562</v>
+        <v>-1.196994668761017</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.354542963909153</v>
+        <v>-1.368399672934068</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.972777787779417</v>
+        <v>-1.951452497865293</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.5485138088277345</v>
+        <v>-0.5947872375093822</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.38506990523568</v>
+        <v>-1.376856880861471</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.608277485709562</v>
+        <v>-1.554801738685378</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8661300883957506</v>
+        <v>-0.8768744782403189</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.8706994021482716</v>
+        <v>-0.8793628781378563</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2.051055713682274</v>
+        <v>-2.103424164908732</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-1.696491604387708</v>
+        <v>-1.67041670338535</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.303318242912968</v>
+        <v>1.283540832532852</v>
       </c>
     </row>
     <row r="4">
@@ -818,7 +818,7 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F4" t="n">
         <v>-0.09401519725900095</v>
@@ -864,43 +864,43 @@
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>0.3860546239676479</v>
+        <v>0.3666474906005819</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-0.1153306758532679</v>
+        <v>-0.1159593120382246</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1499771036719323</v>
+        <v>0.09486284118246982</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.09600647132601053</v>
+        <v>-0.1063710261461267</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.6514819160798689</v>
+        <v>-0.6186297190516271</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.01538065793583716</v>
+        <v>-0.002342922354674511</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1491520137674208</v>
+        <v>0.2308763153054839</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.1898792784850098</v>
+        <v>-0.2081824632678357</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2924175502188048</v>
+        <v>0.2682152260841191</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.03353041487183422</v>
+        <v>-0.03252919940066762</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-0.3087147772404399</v>
+        <v>-0.3093410303212826</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.012733153077933</v>
+        <v>-0.9486260588598381</v>
       </c>
     </row>
     <row r="5">
@@ -919,7 +919,7 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F5" t="n">
         <v>0.0007587433381137274</v>
@@ -934,7 +934,7 @@
         <v>0.5167245559967235</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K5" t="n">
         <v>-0.1130998413203891</v>
@@ -965,43 +965,43 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>0.2045170639298238</v>
+        <v>0.2268121635717584</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-0.001049863446294658</v>
+        <v>0.01517359563954875</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0592666405379092</v>
+        <v>-0.04322712585127975</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.269705091115608</v>
+        <v>-0.2479235615504937</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.395063588347172</v>
+        <v>1.321092352379809</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1293760262886053</v>
+        <v>-0.1086527429139778</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8984969994349373</v>
+        <v>0.9146508327810507</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.2563404105494574</v>
+        <v>-0.2290024301492493</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.4821140983654975</v>
+        <v>-0.4436768737812637</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.3906600473146071</v>
+        <v>-0.3568521108427362</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-0.001850767627551133</v>
+        <v>0.03849782372388157</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.6166039312400379</v>
+        <v>-0.6534355631889164</v>
       </c>
     </row>
     <row r="6">
@@ -1020,7 +1020,7 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>1.412237343162496</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F6" t="n">
         <v>1.043272089906375</v>
@@ -1035,7 +1035,7 @@
         <v>-1.397625998602981</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.73331124061016</v>
+        <v>-1.21822742662512</v>
       </c>
       <c r="K6" t="n">
         <v>-0.514086898314456</v>
@@ -1066,346 +1066,346 @@
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>0.0382030972248047</v>
+        <v>-0.03287917880057725</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>0.8964088007959791</v>
+        <v>0.8723990223760375</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8158076357542</v>
+        <v>1.760758588668794</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.753498562586212</v>
+        <v>1.747440731693861</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2298982358676154</v>
+        <v>0.1307081293392785</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.309215041702351</v>
+        <v>1.312058463588698</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.9757525964158894</v>
+        <v>-0.9480243220126517</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.412912385952343</v>
+        <v>1.401573993745983</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.32187707335843</v>
+        <v>1.343569187325765</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.005340974004832</v>
+        <v>1.999833419294682</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>0.9784788467559364</v>
+        <v>0.9885249899277869</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.4530376284776874</v>
+        <v>-0.3320059723317402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.5109663712257129</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.378337019050345</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01284963915427201</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.43812085720364</v>
+        <v>-0.8595529364901612</v>
       </c>
       <c r="I7" t="n">
-        <v>1.438184337874939</v>
+        <v>0.8595933120444317</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.416307776551107</v>
+        <v>-0.7145804268114895</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7595775587676545</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.105574581396306</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.758752563554639</v>
+        <v>-0.4777515212869103</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.276631879911333</v>
+        <v>-0.2154585555999435</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5616071367219981</v>
+        <v>-0.3227916564190099</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1901125114865394</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.175565777723043</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1208308363061085</v>
+        <v>1.63883830878714</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>0.7353381006551266</v>
+        <v>1.511841637234328</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>-0.009017550057460712</v>
+        <v>0.2050733370106578</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.01425754571295434</v>
+        <v>0.1711041634371105</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0722202347974373</v>
+        <v>-0.002749390350811867</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6584010503112059</v>
+        <v>0.3220947216883759</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.234086530441603</v>
+        <v>-0.004742059571283061</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8121783655272882</v>
+        <v>0.5208941901044097</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1944272360231096</v>
+        <v>-0.05677993537613624</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.7347842240107532</v>
+        <v>0.07418573382958295</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.09221436003096149</v>
+        <v>-0.02333840485530008</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>0.2563046690309104</v>
+        <v>0.1357236145246998</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.222555270959666</v>
+        <v>0.6478197900074567</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>1.339221377233877</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4157521150431646</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4746284463236872</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G8" t="n">
-        <v>2.072004313626362</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04044160684191658</v>
+        <v>-1.43812085720364</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04043717258080222</v>
+        <v>1.438184337874939</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5150989569034282</v>
+        <v>-0.1877805313433304</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6343830154126764</v>
+        <v>-1.416307776551107</v>
       </c>
       <c r="L8" t="n">
-        <v>2.067220434893788</v>
+        <v>0.7595775587676545</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3801870311119669</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N8" t="n">
-        <v>1.374113884096997</v>
+        <v>-0.758752563554639</v>
       </c>
       <c r="O8" t="n">
-        <v>1.03298064947228</v>
+        <v>-1.276631879911333</v>
       </c>
       <c r="P8" t="n">
-        <v>1.157864321459517</v>
+        <v>-0.5616071367219981</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9523436204771309</v>
+        <v>-0.1901125114865394</v>
       </c>
       <c r="R8" t="n">
-        <v>0.599028145432136</v>
+        <v>-1.175565777723043</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.502551779089928</v>
+        <v>-0.1208308363061085</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>2.267414477793932</v>
+        <v>0.6408743282301033</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>0.7032684144555752</v>
+        <v>-0.09457176029226809</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4362924602504121</v>
+        <v>-0.05975359782724542</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5591242699344914</v>
+        <v>0.07120554866420475</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4237930952118625</v>
+        <v>0.5118809904334216</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9616852167439753</v>
+        <v>0.2355594014376566</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.4959502632513858</v>
+        <v>0.8780496960318462</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.9682664038348333</v>
+        <v>-0.2049912739901431</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.5486030459394262</v>
+        <v>-0.7159689110740862</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.5727515272097295</v>
+        <v>-0.08931356127562233</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>0.6570927240350641</v>
+        <v>0.2657158611624624</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7050226511682707</v>
+        <v>2.307755913631371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5109663712257129</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.078975727135832</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.378337019050345</v>
+        <v>0.4746284463236872</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.222643165528982</v>
+        <v>2.072004313626362</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8595529364901612</v>
+        <v>0.04044160684191658</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8595933120444317</v>
+        <v>-0.04043717258080222</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5395937476791089</v>
+        <v>0.2122753221190111</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7145804268114895</v>
+        <v>-0.6343830154126764</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.05769923881117887</v>
+        <v>2.067220434893788</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9754746155400137</v>
+        <v>-0.3801870311119669</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4777515212869103</v>
+        <v>1.374113884096997</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2154585555999435</v>
+        <v>1.03298064947228</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3227916564190099</v>
+        <v>1.157864321459517</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9041475939638333</v>
+        <v>0.9523436204771309</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.157356149683186</v>
+        <v>0.599028145432136</v>
       </c>
       <c r="S9" t="n">
-        <v>1.63883830878714</v>
+        <v>-1.502551779089928</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>1.448433449703462</v>
+        <v>2.165225628954651</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>0.2315198564771405</v>
+        <v>0.7683013280166845</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1238264763500759</v>
+        <v>0.6082449542815018</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002264280617113906</v>
+        <v>0.5596150832883047</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3352983644899755</v>
+        <v>0.5024336238479286</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.01780402886170527</v>
+        <v>0.9433335201752329</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.440269684567982</v>
+        <v>0.40794465178834</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.04657641849082675</v>
+        <v>0.9857227237430525</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.009910787809691764</v>
+        <v>0.6668527900325151</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.04359353315900963</v>
+        <v>0.6822362447846618</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>0.1480742199261749</v>
+        <v>0.6333264196170865</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.5631019837845922</v>
+        <v>0.6906275910973984</v>
       </c>
     </row>
     <row r="10">
@@ -1437,7 +1437,7 @@
         <v>0.5167245559967235</v>
       </c>
       <c r="J10" t="n">
-        <v>1.266968026701548</v>
+        <v>1.085124456945938</v>
       </c>
       <c r="K10" t="n">
         <v>-1.215814248054073</v>
@@ -1466,43 +1466,43 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>-0.2934376330469567</v>
+        <v>-0.2628713979938229</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-1.496668434824395</v>
+        <v>-1.566380594291326</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.062918259884379</v>
+        <v>-2.072427870351774</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.673355311458964</v>
+        <v>-1.712055916468547</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6605647709671663</v>
+        <v>0.6893538978107264</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.284838449558866</v>
+        <v>-2.340265789375291</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3319444149836105</v>
+        <v>0.2504148496684337</v>
       </c>
       <c r="AD10" t="n">
-        <v>-2.336837578817556</v>
+        <v>-2.353769343414925</v>
       </c>
       <c r="AE10" t="n">
-        <v>-2.537318296389998</v>
+        <v>-2.56506783291362</v>
       </c>
       <c r="AF10" t="n">
-        <v>-2.214252909434993</v>
+        <v>-2.245036594766701</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>-2.010369648506034</v>
+        <v>-2.045940823497894</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.06093380452166856</v>
+        <v>-0.02247444157545526</v>
       </c>
     </row>
     <row r="11">
@@ -1521,7 +1521,7 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E11" t="n">
-        <v>3.239126928047936</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F11" t="n">
         <v>2.085785436474636</v>
@@ -1536,7 +1536,7 @@
         <v>0.1738557999490154</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3696241010989402</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K11" t="n">
         <v>-1.61680130504814</v>
@@ -1563,47 +1563,47 @@
         <v>1.297229033230895</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2390627541586076</v>
+        <v>0.2345780457845026</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>0.3228803617050509</v>
+        <v>0.3320864105621214</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>1.010121021362002</v>
+        <v>0.9584212836373204</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.05328408987608018</v>
+        <v>-0.009212275318014239</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.64220962519623</v>
+        <v>0.64803460794662</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.349027811219843</v>
+        <v>-1.289618497388059</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5257096023916737</v>
+        <v>0.5250348352143922</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.110488425295298</v>
+        <v>-1.185777439329283</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.117031411325065</v>
+        <v>1.145900422751489</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.21503172483887</v>
+        <v>1.136840388875925</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.8188214412314514</v>
+        <v>0.7460471477817401</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>0.854237193884324</v>
+        <v>0.8392152531009947</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.736720046983518</v>
+        <v>0.698157774976528</v>
       </c>
     </row>
     <row r="12">
@@ -1622,7 +1622,7 @@
         <v>2.393718654096563</v>
       </c>
       <c r="E12" t="n">
-        <v>1.080075600456052</v>
+        <v>0.5818329863963865</v>
       </c>
       <c r="F12" t="n">
         <v>0.8537242087121459</v>
@@ -1668,43 +1668,43 @@
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>0.9417216513541262</v>
+        <v>0.9711662178089645</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.1040160957581647</v>
+        <v>0.07663496150480353</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.410538204989231</v>
+        <v>1.409800751059402</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2300262513629699</v>
+        <v>0.2346691372621008</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.901341387509475</v>
+        <v>0.9136767431912179</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8489564409995877</v>
+        <v>0.8947189859077489</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.5597232441256664</v>
+        <v>-0.5315881218224262</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9716201126751248</v>
+        <v>0.9954614587313523</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.7238307244034425</v>
+        <v>0.679236937270401</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2336690314343652</v>
+        <v>0.2382916859409214</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>0.1903662291174423</v>
+        <v>0.1929139405145071</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.3713497196330051</v>
+        <v>0.2339455726560332</v>
       </c>
     </row>
     <row r="13">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C13" t="n">
         <v>1.63494810752045</v>
@@ -1772,7 +1772,7 @@
         <v>2.393718654096563</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5818329863963865</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F14" t="n">
         <v>0.5694023869208018</v>
@@ -1818,43 +1818,43 @@
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>-1.337339250556195</v>
+        <v>-1.251248975902584</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>0.003196817750909093</v>
+        <v>0.01946609249702566</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6967633721998642</v>
+        <v>0.7714120596359753</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.07357918039973244</v>
+        <v>0.06899296595429134</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.02586108042951074</v>
+        <v>0.02626367025341976</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5007488818552442</v>
+        <v>0.4099971026400017</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1.267359271509478</v>
+        <v>-1.509036197265181</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.9355292244728864</v>
+        <v>0.9425219603635665</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.9431595477319474</v>
+        <v>1.002125204403756</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.08125773525704162</v>
+        <v>0.1062217580317536</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>0.1171373177325492</v>
+        <v>0.1149901643125172</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.134291827673825</v>
+        <v>-1.164323460044918</v>
       </c>
     </row>
     <row r="15">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C15" t="n">
         <v>-0.7763621548162278</v>
@@ -1872,15 +1872,9 @@
       <c r="D15" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E15" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.42468057404869</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1915,20 +1909,20 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.886300587034986</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C16" t="n">
-        <v>1.559120740780303</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D16" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F16" t="n">
         <v>-0.1887891378561156</v>
@@ -1945,9 +1939,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>-3.044872614579567</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1968,27 +1960,25 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C17" t="n">
-        <v>1.657696317542495</v>
+        <v>1.559120740780303</v>
       </c>
       <c r="D17" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F17" t="n">
         <v>-0.1887891378561156</v>
       </c>
-      <c r="G17" t="n">
-        <v>-0.398981295740146</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -2000,7 +1990,9 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>-3.044872614579567</v>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -2021,125 +2013,67 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.819875174399046</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8994226501410234</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D18" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E18" t="n">
-        <v>-0.08249049901650093</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.1903066245323431</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.398981295740146</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-1.973831894901305</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.973916769199483</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.7214373174347188</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.08739368717664438</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.824104133701805</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-1.855341996794555</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.484547863495486</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-1.994500018539928</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.666027818422636</v>
-      </c>
-      <c r="R18" t="n">
-        <v>5.079150508807505</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-1.241284315154525</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
-        <v>0.8611545575048254</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.04476414701330287</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-0.04737847572472226</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.3639747202648466</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.05088238108044116</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.407969587555722</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-1.226265615173698</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>-0.1010456084763366</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>-0.01447896013977084</v>
-      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.1491037240698987</v>
-      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C19" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D19" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E19" t="n">
-        <v>-0.4146522417229446</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.0007587433381137274</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -2173,23 +2107,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.819875174399046</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C20" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D20" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1887891378561156</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -2224,23 +2158,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C21" t="n">
-        <v>1.657696317542495</v>
+        <v>1.225480327123656</v>
       </c>
       <c r="D21" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08359037233672091</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2850805651294578</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -2254,7 +2188,9 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>-3.0212742629983</v>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -2275,25 +2211,27 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C22" t="n">
-        <v>1.225480327123656</v>
+        <v>1.020746436925259</v>
       </c>
       <c r="D22" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.398981295740146</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2306,7 +2244,7 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>-3.0212742629983</v>
+        <v>-2.85758410996637</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -2328,14 +2266,14 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C23" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D23" t="n">
         <v>2.393718654096563</v>
@@ -2375,27 +2313,25 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C24" t="n">
-        <v>1.657696317542495</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D24" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08359037233672091</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2850805651294578</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.42468057404869</v>
-      </c>
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2407,7 +2343,9 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>-2.461937143971006</v>
+      </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2428,24 +2366,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C25" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D25" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E25" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.09553268393522843</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2479,27 +2413,25 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C26" t="n">
-        <v>1.020746436925259</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D26" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.09401519725900095</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.398981295740146</v>
-      </c>
+        <v>0.2850805651294578</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -2511,9 +2443,7 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>-2.85758410996637</v>
-      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2534,27 +2464,21 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C27" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D27" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E27" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.42468057404869</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -2587,21 +2511,25 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C28" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D28" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.42468057404869</v>
+      </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2634,168 +2562,162 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.886300587034986</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.056923411754772</v>
+        <v>0.8994226501410234</v>
       </c>
       <c r="D29" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1.973831894901305</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.973916769199483</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7214373174347188</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.08739368717664438</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.824104133701805</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1.855341996794555</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4.484547863495486</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-1.994500018539928</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.666027818422636</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5.079150508807505</v>
+      </c>
       <c r="S29" t="n">
-        <v>-2.461937143971006</v>
+        <v>-1.241284315154525</v>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0.7769769588486537</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
+      <c r="X29" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.06833362283931665</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-0.04715218145994972</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.4340628507515836</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.06727013847007454</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.389960093165063</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-1.231317180307368</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>-0.1316614231249538</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0.01589503549431402</v>
+      </c>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
+      <c r="AH29" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.0762867368325241</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.819875174399046</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.9962615183626544</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D30" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.2496712436899428</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.3798545057265725</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.626146278427006</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-1.626205169301453</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-1.516554540799623</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.849279955539432</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.777110500812665</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-1.596085441209226</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.11010122539892</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>-5.188358088827596</v>
-      </c>
-      <c r="R30" t="n">
-        <v>-3.066526515511348</v>
-      </c>
-      <c r="S30" t="n">
-        <v>-4.133767980400661</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="n">
-        <v>-0.6483253687333674</v>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>-0.4442004294320974</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>-0.08147985949313452</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.5279436335292526</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>-0.5410425272638165</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>-0.3035740028029867</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>-0.5357857347618424</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>-0.6631304724287659</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>-0.1011952941460156</v>
-      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.06232152976493142</v>
-      </c>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.819875174399046</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C31" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D31" t="n">
         <v>2.393718654096563</v>
@@ -2835,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C32" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D32" t="n">
         <v>2.393718654096563</v>
@@ -2882,14 +2804,14 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C33" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D33" t="n">
         <v>2.393718654096563</v>
@@ -2929,14 +2851,14 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C34" t="n">
-        <v>1.013163700251244</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D34" t="n">
         <v>2.393718654096563</v>
@@ -2955,9 +2877,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="n">
-        <v>-2.971127765888117</v>
-      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
@@ -2978,14 +2898,14 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C35" t="n">
-        <v>1.657696317542495</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D35" t="n">
         <v>2.393718654096563</v>
@@ -3004,7 +2924,9 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>-2.971127765888117</v>
+      </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
@@ -3025,71 +2947,121 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.886300587034986</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C36" t="n">
-        <v>1.657696317542495</v>
+        <v>-0.9962615183626544</v>
       </c>
       <c r="D36" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3798545057265725</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.626146278427006</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-1.626205169301453</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1.516554540799623</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.849279955539432</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.777110500812665</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-1.596085441209226</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.11010122539892</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-5.188358088827596</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-3.066526515511348</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-4.133767980400661</v>
+      </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>-0.5548544149366031</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
+      <c r="X36" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-0.4410945860044058</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-0.0833673659496012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.4642756166093543</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.5381502340637936</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-0.2434524395904746</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.5861339983204222</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>-0.5765295797458112</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>-0.0939910387720447</v>
+      </c>
       <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
+      <c r="AH36" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>-0.06131758470958937</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.886300587034986</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C37" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D37" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E37" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.09553268393522843</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -3123,20 +3095,24 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C38" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D38" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>-0.4146522417229446</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1903066245323431</v>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -3170,14 +3146,14 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C39" t="n">
-        <v>1.559120740780303</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D39" t="n">
         <v>2.393718654096563</v>
@@ -3186,7 +3162,7 @@
         <v>-0.5807331130761665</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.09401519725900095</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -3200,9 +3176,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>-2.176790395697422</v>
-      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
@@ -3223,24 +3197,20 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.819875174399046</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C40" t="n">
-        <v>1.657696317542495</v>
+        <v>1.559120740780303</v>
       </c>
       <c r="D40" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E40" t="n">
-        <v>-0.08249049901650093</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.1903066245323431</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -3253,7 +3223,9 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>-2.176790395697422</v>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
@@ -3274,24 +3246,20 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.886300587034986</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C41" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D41" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E41" t="n">
-        <v>-0.7468139844293883</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-0.1887891378561156</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -3325,24 +3293,20 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C42" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D42" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E42" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.09553268393522843</v>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -3376,14 +3340,14 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.886300587034986</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C43" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D43" t="n">
         <v>2.393718654096563</v>
@@ -3423,14 +3387,14 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C44" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D44" t="n">
         <v>2.393718654096563</v>
@@ -3470,24 +3434,20 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.886300587034986</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C45" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D45" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E45" t="n">
-        <v>-0.5807331130761665</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-0.09401519725900095</v>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3521,14 +3481,14 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.819875174399046</v>
+        <v>1.974867803882906</v>
       </c>
       <c r="C46" t="n">
-        <v>1.657696317542495</v>
+        <v>1.688027264238553</v>
       </c>
       <c r="D46" t="n">
         <v>2.393718654096563</v>
@@ -3581,7 +3541,7 @@
         <v>0.4607755271036255</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5818329863963865</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F47" t="n">
         <v>0.5694023869208018</v>
@@ -3596,7 +3556,7 @@
         <v>0.7738761230325046</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3577501779234991</v>
+        <v>0.5395937476791089</v>
       </c>
       <c r="K47" t="n">
         <v>0.9896145654132948</v>
@@ -3627,43 +3587,43 @@
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="n">
-        <v>1.17709746631509</v>
+        <v>1.177667183298397</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
-        <v>-0.7582629159433542</v>
+        <v>-0.8814381223507793</v>
       </c>
       <c r="Y47" t="n">
-        <v>-0.9838590465919386</v>
+        <v>-1.087988444829415</v>
       </c>
       <c r="Z47" t="n">
-        <v>-1.646591034896806</v>
+        <v>-1.61201535498451</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.1275690530045329</v>
+        <v>-0.2185460254212024</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1.055394524480779</v>
+        <v>-1.046873071079643</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.8748575956025506</v>
+        <v>-0.8643261033062383</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.643766612940987</v>
+        <v>-0.6358497782340311</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.7966809484792116</v>
+        <v>-0.8484430187663308</v>
       </c>
       <c r="AF47" t="n">
-        <v>-1.769863154857676</v>
+        <v>-1.895028643078849</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>-1.128480060063442</v>
+        <v>-1.105080967679231</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.587196400350206</v>
+        <v>1.534786137900541</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/england/data_preparation/df_selected.xlsx
+++ b/p6_deployment/data/england/data_preparation/df_selected.xlsx
@@ -732,7 +732,7 @@
         <v>0.5452969523340327</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2971356546716294</v>
+        <v>0.4789792244272392</v>
       </c>
       <c r="K3" t="n">
         <v>1.357186034324523</v>
@@ -763,43 +763,43 @@
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>0.4219651718836091</v>
+        <v>0.3121053595335355</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-1.196994668761017</v>
+        <v>-1.224201137925904</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.368399672934068</v>
+        <v>-1.410129093411008</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.951452497865293</v>
+        <v>-1.993814492722347</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.5947872375093822</v>
+        <v>-0.5986559046118181</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.376856880861471</v>
+        <v>-1.411785146322436</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.554801738685378</v>
+        <v>-1.645640875674063</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8768744782403189</v>
+        <v>-0.8921519072992897</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.8793628781378563</v>
+        <v>-0.9022555148124438</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2.103424164908732</v>
+        <v>-2.122592165704877</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-1.67041670338535</v>
+        <v>-1.728931513975355</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.283540832532852</v>
+        <v>1.283931335996497</v>
       </c>
     </row>
     <row r="4">
@@ -864,43 +864,43 @@
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>0.3666474906005819</v>
+        <v>0.299588913698293</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-0.1159593120382246</v>
+        <v>-0.1371968681964333</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09486284118246982</v>
+        <v>0.07697843419222514</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1063710261461267</v>
+        <v>-0.09682031532781767</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.6186297190516271</v>
+        <v>-0.5926747454746231</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.002342922354674511</v>
+        <v>0.01834574143529453</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2308763153054839</v>
+        <v>0.2202771008883722</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.2081824632678357</v>
+        <v>-0.1926522599588997</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2682152260841191</v>
+        <v>0.2570233689241815</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.03252919940066762</v>
+        <v>-0.06047289497370743</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-0.3093410303212826</v>
+        <v>-0.2992762486648831</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.9486260588598381</v>
+        <v>-0.8399994474895361</v>
       </c>
     </row>
     <row r="5">
@@ -965,43 +965,43 @@
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>0.2268121635717584</v>
+        <v>0.3177831012299182</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>0.01517359563954875</v>
+        <v>0.06439475024434588</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.04322712585127975</v>
+        <v>-0.02592700599265186</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2479235615504937</v>
+        <v>-0.2935681647769423</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.321092352379809</v>
+        <v>1.311884984092761</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1086527429139778</v>
+        <v>-0.1949593674594895</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.9146508327810507</v>
+        <v>0.8286887001068362</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.2290024301492493</v>
+        <v>-0.268336569534327</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.4436768737812637</v>
+        <v>-0.4312890917822899</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.3568521108427362</v>
+        <v>-0.3196051672913867</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0.03849782372388157</v>
+        <v>-0.02994269153963446</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.6534355631889164</v>
+        <v>-0.6915670560254653</v>
       </c>
     </row>
     <row r="6">
@@ -1035,7 +1035,7 @@
         <v>-1.397625998602981</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.21822742662512</v>
+        <v>-0.8545402871139001</v>
       </c>
       <c r="K6" t="n">
         <v>-0.514086898314456</v>
@@ -1066,346 +1066,346 @@
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>-0.03287917880057725</v>
+        <v>0.04564642919183598</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>0.8723990223760375</v>
+        <v>0.8579068055738028</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.760758588668794</v>
+        <v>1.752497315098807</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.747440731693861</v>
+        <v>1.820342070770335</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1307081293392785</v>
+        <v>0.1253364572702831</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.312058463588698</v>
+        <v>1.357634665959755</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.9480243220126517</v>
+        <v>-0.9524870271204698</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.401573993745983</v>
+        <v>1.438603071349568</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.343569187325765</v>
+        <v>1.336671537752975</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.999833419294682</v>
+        <v>1.977436376004106</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>0.9885249899277869</v>
+        <v>1.025360848224572</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.3320059723317402</v>
+        <v>-0.417912536648558</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.5109663712257129</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.378337019050345</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.222643165528982</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8595529364901612</v>
+        <v>-1.43812085720364</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8595933120444317</v>
+        <v>1.438184337874939</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7145804268114895</v>
+        <v>-1.416307776551107</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05769923881117887</v>
+        <v>0.7595775587676545</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9754746155400137</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4777515212869103</v>
+        <v>-0.758752563554639</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2154585555999435</v>
+        <v>-1.276631879911333</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3227916564190099</v>
+        <v>-0.5616071367219981</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9041475939638333</v>
+        <v>-0.1901125114865394</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.157356149683186</v>
+        <v>-1.175565777723043</v>
       </c>
       <c r="S7" t="n">
-        <v>1.63883830878714</v>
+        <v>-0.1208308363061085</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>1.511841637234328</v>
+        <v>0.6623174778209597</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>0.2050733370106578</v>
+        <v>-0.1273031985113343</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1711041634371105</v>
+        <v>-0.05450943459587675</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.002749390350811867</v>
+        <v>0.06897820055755884</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3220947216883759</v>
+        <v>0.5763765380341489</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.004742059571283061</v>
+        <v>0.2273510979158995</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5208941901044097</v>
+        <v>0.8695091216852507</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.05677993537613624</v>
+        <v>-0.1918233796270364</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.07418573382958295</v>
+        <v>-0.7639113608425089</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.02333840485530008</v>
+        <v>-0.1051291630014064</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>0.1357236145246998</v>
+        <v>0.2776370358799312</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.6478197900074567</v>
+        <v>2.296318168869189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7477679166607292</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08249049901650093</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1903066245323431</v>
+        <v>0.4746284463236872</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01284963915427201</v>
+        <v>2.072004313626362</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.43812085720364</v>
+        <v>0.04044160684191658</v>
       </c>
       <c r="I8" t="n">
-        <v>1.438184337874939</v>
+        <v>-0.04043717258080222</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1877805313433304</v>
+        <v>-0.1514118173922085</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.416307776551107</v>
+        <v>-0.6343830154126764</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7595775587676545</v>
+        <v>2.067220434893788</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.105574581396306</v>
+        <v>-0.3801870311119669</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.758752563554639</v>
+        <v>1.374113884096997</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.276631879911333</v>
+        <v>1.03298064947228</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5616071367219981</v>
+        <v>1.157864321459517</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1901125114865394</v>
+        <v>0.9523436204771309</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.175565777723043</v>
+        <v>0.599028145432136</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1208308363061085</v>
+        <v>-1.502551779089928</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>0.6408743282301033</v>
+        <v>2.165225628954651</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>-0.09457176029226809</v>
+        <v>0.7683013280166845</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.05975359782724542</v>
+        <v>0.6082449542815018</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.07120554866420475</v>
+        <v>0.5596150832883047</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5118809904334216</v>
+        <v>0.5024336238479286</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2355594014376566</v>
+        <v>0.9433335201752329</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.8780496960318462</v>
+        <v>0.40794465178834</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.2049912739901431</v>
+        <v>0.9857227237430525</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.7159689110740862</v>
+        <v>0.6668527900325151</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.08931356127562233</v>
+        <v>0.6822362447846618</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>0.2657158611624624</v>
+        <v>0.6333264196170865</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.307755913631371</v>
+        <v>0.6906275910973984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C9" t="n">
-        <v>1.339221377233877</v>
+        <v>-0.5109663712257129</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4746284463236872</v>
+        <v>-0.378337019050345</v>
       </c>
       <c r="G9" t="n">
-        <v>2.072004313626362</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04044160684191658</v>
+        <v>-0.8595529364901612</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04043717258080222</v>
+        <v>0.8595933120444317</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2122753221190111</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6343830154126764</v>
+        <v>-0.7145804268114895</v>
       </c>
       <c r="L9" t="n">
-        <v>2.067220434893788</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3801870311119669</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N9" t="n">
-        <v>1.374113884096997</v>
+        <v>-0.4777515212869103</v>
       </c>
       <c r="O9" t="n">
-        <v>1.03298064947228</v>
+        <v>-0.2154585555999435</v>
       </c>
       <c r="P9" t="n">
-        <v>1.157864321459517</v>
+        <v>-0.3227916564190099</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9523436204771309</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R9" t="n">
-        <v>0.599028145432136</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.502551779089928</v>
+        <v>1.63883830878714</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>2.165225628954651</v>
+        <v>1.511841637234328</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>0.7683013280166845</v>
+        <v>0.2050733370106578</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6082449542815018</v>
+        <v>0.1711041634371105</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5596150832883047</v>
+        <v>-0.002749390350811867</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5024336238479286</v>
+        <v>0.3220947216883759</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9433335201752329</v>
+        <v>-0.004742059571283061</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.40794465178834</v>
+        <v>0.5208941901044097</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9857227237430525</v>
+        <v>-0.05677993537613624</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.6668527900325151</v>
+        <v>0.07418573382958295</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.6822362447846618</v>
+        <v>-0.02333840485530008</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>0.6333264196170865</v>
+        <v>0.1357236145246998</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.6906275910973984</v>
+        <v>0.6478197900074567</v>
       </c>
     </row>
     <row r="10">
@@ -1437,7 +1437,7 @@
         <v>0.5167245559967235</v>
       </c>
       <c r="J10" t="n">
-        <v>1.085124456945938</v>
+        <v>1.266968026701548</v>
       </c>
       <c r="K10" t="n">
         <v>-1.215814248054073</v>
@@ -1536,7 +1536,7 @@
         <v>0.1738557999490154</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.1877805313433304</v>
       </c>
       <c r="K11" t="n">
         <v>-1.61680130504814</v>
@@ -1563,7 +1563,7 @@
         <v>1.297229033230895</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2345780457845026</v>
+        <v>0.2480750770005946</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
@@ -1710,11 +1710,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.974867803882906</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C13" t="n">
         <v>1.63494810752045</v>
@@ -1722,48 +1722,100 @@
       <c r="D13" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0.4157521150431646</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5694023869208018</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.669003161442819</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.669063763807416</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.915073955308523</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2147263603817656</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.440313973089069</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.434426302925192</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.451574971172967</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.03543156403547253</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.428016124263538</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5.079150508807505</v>
+      </c>
       <c r="S13" t="n">
-        <v>-2.859456995012502</v>
+        <v>-2.286354170896134</v>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>-1.251248975902584</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.01946609249702566</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7714120596359753</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.06899296595429134</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.02626367025341976</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.4099971026400017</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.509036197265181</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9425219603635665</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.002125204403756</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.1062217580317536</v>
+      </c>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
+      <c r="AH13" t="n">
+        <v>0.1149901643125172</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-1.164323460044918</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.819875174399046</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C14" t="n">
         <v>1.63494810752045</v>
@@ -1771,91 +1823,39 @@
       <c r="D14" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E14" t="n">
-        <v>0.4157521150431646</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.5694023869208018</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.669003161442819</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-1.669063763807416</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.73331124061016</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.915073955308523</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2147263603817656</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.440313973089069</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.434426302925192</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.451574971172967</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.03543156403547253</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.428016124263538</v>
-      </c>
-      <c r="R14" t="n">
-        <v>5.079150508807505</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-2.286354170896134</v>
+        <v>-2.859456995012502</v>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>-1.251248975902584</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="n">
-        <v>0.01946609249702566</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.7714120596359753</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.06899296595429134</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.02626367025341976</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.4099971026400017</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-1.509036197265181</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.9425219603635665</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.002125204403756</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.1062217580317536</v>
-      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="n">
-        <v>0.1149901643125172</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-1.164323460044918</v>
-      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C15" t="n">
         <v>-0.7763621548162278</v>
@@ -1909,14 +1909,14 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.819875174399046</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C16" t="n">
-        <v>1.688027264238553</v>
+        <v>1.559120740780303</v>
       </c>
       <c r="D16" t="n">
         <v>2.393718654096563</v>
@@ -1939,7 +1939,9 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-3.044872614579567</v>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1960,23 +1962,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C17" t="n">
-        <v>1.559120740780303</v>
+        <v>1.225480327123656</v>
       </c>
       <c r="D17" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1887891378561156</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1991,7 +1993,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-3.044872614579567</v>
+        <v>-3.0212742629983</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -2013,67 +2015,125 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.974867803882906</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C18" t="n">
-        <v>1.688027264238553</v>
+        <v>0.8994226501410234</v>
       </c>
       <c r="D18" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.973831894901305</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.973916769199483</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7214373174347188</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.08739368717664438</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.824104133701805</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.855341996794555</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.484547863495486</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.994500018539928</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.666027818422636</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5.079150508807505</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.241284315154525</v>
+      </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>0.7769769588486537</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.06833362283931665</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.04715218145994972</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.4340628507515836</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.06727013847007454</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.389960093165063</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-1.231317180307368</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.1316614231249538</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.01589503549431402</v>
+      </c>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.0762867368325241</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.974867803882906</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C19" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D19" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.1887891378561156</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -2111,10 +2171,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C20" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D20" t="n">
         <v>2.393718654096563</v>
@@ -2158,24 +2218,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C21" t="n">
-        <v>1.225480327123656</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D21" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E21" t="n">
-        <v>-0.2485713703697228</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.09553268393522843</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -2188,9 +2244,7 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>-3.0212742629983</v>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -2211,27 +2265,21 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C22" t="n">
-        <v>1.020746436925259</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D22" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E22" t="n">
-        <v>-0.5807331130761665</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.09401519725900095</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.398981295740146</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2243,9 +2291,7 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>-2.85758410996637</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2266,20 +2312,24 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C23" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D23" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2850805651294578</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -2313,25 +2363,27 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.056923411754772</v>
+        <v>1.020746436925259</v>
       </c>
       <c r="D24" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.398981295740146</v>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2344,7 +2396,7 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>-2.461937143971006</v>
+        <v>-2.85758410996637</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -2366,14 +2418,14 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C25" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D25" t="n">
         <v>2.393718654096563</v>
@@ -2413,25 +2465,25 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C26" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D26" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E26" t="n">
-        <v>-0.08249049901650093</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>0.2850805651294578</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.42468057404869</v>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -2464,14 +2516,14 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C27" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D27" t="n">
         <v>2.393718654096563</v>
@@ -2511,25 +2563,21 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C28" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D28" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>0.09553268393522843</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.42468057404869</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -2562,115 +2610,67 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.819875174399046</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8994226501410234</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D29" t="n">
         <v>2.393718654096563</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1903066245323431</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.398981295740146</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-1.973831894901305</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.973916769199483</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.7214373174347188</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.08739368717664438</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.824104133701805</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1.855341996794555</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4.484547863495486</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-1.994500018539928</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.666027818422636</v>
-      </c>
-      <c r="R29" t="n">
-        <v>5.079150508807505</v>
-      </c>
+        <v>0.09553268393522843</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>-1.241284315154525</v>
+        <v>-2.461937143971006</v>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="n">
-        <v>0.7769769588486537</v>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.06833362283931665</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>-0.04715218145994972</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.4340628507515836</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.06727013847007454</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.389960093165063</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>-1.231317180307368</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>-0.1316614231249538</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>-0.01589503549431402</v>
-      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.0762867368325241</v>
-      </c>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C30" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D30" t="n">
         <v>2.393718654096563</v>
@@ -2710,14 +2710,14 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.974867803882906</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C31" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D31" t="n">
         <v>2.393718654096563</v>
@@ -2757,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C32" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D32" t="n">
         <v>2.393718654096563</v>
@@ -2804,49 +2804,103 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.974867803882906</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C33" t="n">
-        <v>1.688027264238553</v>
+        <v>-0.9962615183626544</v>
       </c>
       <c r="D33" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3798545057265725</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.626146278427006</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-1.626205169301453</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-1.516554540799623</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.849279955539432</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.777110500812665</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-1.596085441209226</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.11010122539892</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-5.188358088827596</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-3.066526515511348</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-4.133767980400661</v>
+      </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>-0.5548544149366031</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
+      <c r="X33" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.4410945860044058</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.0833673659496012</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.4642756166093543</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-0.5381502340637936</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-0.2434524395904746</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.5861339983204222</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>-0.5765295797458112</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-0.0939910387720447</v>
+      </c>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
+      <c r="AH33" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-0.06131758470958937</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2855,10 +2909,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C34" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D34" t="n">
         <v>2.393718654096563</v>
@@ -2898,14 +2952,14 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C35" t="n">
-        <v>1.013163700251244</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D35" t="n">
         <v>2.393718654096563</v>
@@ -2924,9 +2978,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
-        <v>-2.971127765888117</v>
-      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
@@ -2947,115 +2999,63 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.819875174399046</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.9962615183626544</v>
+        <v>1.559120740780303</v>
       </c>
       <c r="D36" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E36" t="n">
-        <v>0.08359037233672091</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.3798545057265725</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.626146278427006</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-1.626205169301453</v>
-      </c>
-      <c r="J36" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-1.516554540799623</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1.849279955539432</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.777110500812665</v>
-      </c>
-      <c r="O36" t="n">
-        <v>-1.596085441209226</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.11010122539892</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-5.188358088827596</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-3.066526515511348</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>-4.133767980400661</v>
+        <v>-2.176790395697422</v>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="n">
-        <v>-0.5548544149366031</v>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>-0.4410945860044058</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>-0.0833673659496012</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.4642756166093543</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-0.5381502340637936</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>-0.2434524395904746</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-0.5861339983204222</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>-0.5765295797458112</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>-0.0939910387720447</v>
-      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>-0.06131758470958937</v>
-      </c>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.819875174399046</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C37" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D37" t="n">
         <v>2.393718654096563</v>
@@ -3102,7 +3102,7 @@
         <v>1.819875174399046</v>
       </c>
       <c r="C38" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D38" t="n">
         <v>2.393718654096563</v>
@@ -3146,24 +3146,20 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C39" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D39" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E39" t="n">
-        <v>-0.5807331130761665</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.1887891378561156</v>
-      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -3197,14 +3193,14 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C40" t="n">
-        <v>1.559120740780303</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D40" t="n">
         <v>2.393718654096563</v>
@@ -3223,9 +3219,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>-2.176790395697422</v>
-      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
@@ -3246,20 +3240,24 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.819875174399046</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C41" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D41" t="n">
         <v>2.393718654096563</v>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.1887891378561156</v>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -3293,14 +3291,14 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C42" t="n">
-        <v>1.688027264238553</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D42" t="n">
         <v>2.393718654096563</v>
@@ -3319,7 +3317,9 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>-2.971127765888117</v>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -3340,14 +3340,14 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.974867803882906</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C43" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D43" t="n">
         <v>2.393718654096563</v>
@@ -3394,7 +3394,7 @@
         <v>1.819875174399046</v>
       </c>
       <c r="C44" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D44" t="n">
         <v>2.393718654096563</v>
@@ -3441,7 +3441,7 @@
         <v>1.819875174399046</v>
       </c>
       <c r="C45" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D45" t="n">
         <v>2.393718654096563</v>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.974867803882906</v>
+        <v>2.019151412306866</v>
       </c>
       <c r="C46" t="n">
-        <v>1.688027264238553</v>
+        <v>1.703192737586583</v>
       </c>
       <c r="D46" t="n">
         <v>2.393718654096563</v>
@@ -3587,43 +3587,43 @@
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="n">
-        <v>1.177667183298397</v>
+        <v>1.067807370948323</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
-        <v>-0.8814381223507793</v>
+        <v>-0.908644591515666</v>
       </c>
       <c r="Y47" t="n">
-        <v>-1.087988444829415</v>
+        <v>-1.129717865306354</v>
       </c>
       <c r="Z47" t="n">
-        <v>-1.61201535498451</v>
+        <v>-1.654377349841564</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.2185460254212024</v>
+        <v>-0.2224146925236383</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1.046873071079643</v>
+        <v>-1.081801336540609</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.8643261033062383</v>
+        <v>-0.9551652402949236</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.6358497782340311</v>
+        <v>-0.6511272072930019</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.8484430187663308</v>
+        <v>-0.8713356554409183</v>
       </c>
       <c r="AF47" t="n">
-        <v>-1.895028643078849</v>
+        <v>-1.914196643874994</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="n">
-        <v>-1.105080967679231</v>
+        <v>-1.163595778269236</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.534786137900541</v>
+        <v>1.535176641364186</v>
       </c>
     </row>
   </sheetData>
